--- a/Max_Function.xlsx
+++ b/Max_Function.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Preeti(EXCEL)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B63EFFB-A1FB-47B8-98CB-A3CD8933E3F0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ACF1C05-F946-4B59-9320-B3A03D1EE62D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" activeTab="2" xr2:uid="{EC790C15-DB7C-4D65-AE93-28E649B9A23F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" firstSheet="1" activeTab="3" xr2:uid="{EC790C15-DB7C-4D65-AE93-28E649B9A23F}"/>
   </bookViews>
   <sheets>
     <sheet name="Maxifs with one condition" sheetId="1" r:id="rId1"/>
     <sheet name="Mexifs with multiple condition" sheetId="2" r:id="rId2"/>
     <sheet name="Maxifs with logical operaters" sheetId="3" r:id="rId3"/>
+    <sheet name="Maxifs with wildcard chart" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="32">
   <si>
     <t>Name</t>
   </si>
@@ -114,6 +115,15 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Age between</t>
+  </si>
+  <si>
+    <t>Sports Excludind</t>
+  </si>
+  <si>
+    <t>boll</t>
   </si>
 </sst>
 </file>
@@ -161,7 +171,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -184,11 +194,46 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -196,6 +241,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1108,9 +1165,599 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D0E9812-FDD7-40FD-9049-EB6B13C77BB4}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="7"/>
+      <c r="G1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H1" s="1">
+        <v>13</v>
+      </c>
+      <c r="I1" s="1">
+        <v>14</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="5">
+        <v>156</v>
+      </c>
+      <c r="F2" s="8"/>
+      <c r="G2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="12"/>
+      <c r="I2" s="13"/>
+      <c r="K2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="1">
+        <f>_xlfn.MAXIFS(D2:D17,B2:B17,"&lt;&gt;"&amp;L1)</f>
+        <v>173</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="5">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="5">
+        <v>173</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="1">
+        <v>13</v>
+      </c>
+      <c r="I4" s="1">
+        <v>14</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="5">
+        <v>170</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="10"/>
+      <c r="I5" s="11"/>
+      <c r="K5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" s="1">
+        <f>_xlfn.MINIFS(D2:D17,B2:B17,"&lt;&gt;"&amp;L4)</f>
+        <v>156</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="5">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="5">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="5">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="5">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="5">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="5">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="5">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="5">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="5">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="5">
+        <v>171</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{135F9775-DBDE-487A-A10F-9220FF2AB63B}">
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="5">
+        <v>156</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2">
+        <f>_xlfn.MAXIFS(D2:D17,B2:B17,"*"&amp;H1)</f>
+        <v>173</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="5">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="5">
+        <v>173</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="5">
+        <v>170</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5">
+        <f>_xlfn.MINIFS(D2:D17,B2:B17,"*"&amp;H4)</f>
+        <v>156</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="5">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="5">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="5">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="5">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="5">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="5">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="5">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="5">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="5">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="5">
+        <v>171</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>